--- a/financial/UNLID_財務モデル_v4.9.xlsx
+++ b/financial/UNLID_財務モデル_v4.9.xlsx
@@ -8283,7 +8283,7 @@
     <row r="4">
       <c r="A4" s="36" t="inlineStr">
         <is>
-          <t>▌月商マトリックス（万円/月）  ─  単価：20万円/社 固定</t>
+          <t>▌月商マトリックス（万円/月）  ─  単価：24万円/社 固定</t>
         </is>
       </c>
     </row>
@@ -8300,12 +8300,12 @@
       </c>
       <c r="C5" s="37" t="inlineStr">
         <is>
-          <t>5社</t>
+          <t>5社 ★BEP</t>
         </is>
       </c>
       <c r="D5" s="33" t="inlineStr">
         <is>
-          <t>6社 ★BEP</t>
+          <t>6社</t>
         </is>
       </c>
       <c r="E5" s="37" t="inlineStr">
@@ -8326,19 +8326,19 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>160</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7">
@@ -8348,19 +8348,19 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="D7" s="38" t="n">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>280</v>
+        <v>336</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>320</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8">
@@ -8370,19 +8370,19 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="D8" s="38" t="n">
-        <v>360</v>
+        <v>432</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>420</v>
+        <v>504</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>480</v>
+        <v>576</v>
       </c>
     </row>
     <row r="9">
@@ -8392,19 +8392,19 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>320</v>
+        <v>384</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>400</v>
+        <v>480</v>
       </c>
       <c r="D9" s="38" t="n">
-        <v>480</v>
+        <v>576</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>560</v>
+        <v>672</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>640</v>
+        <v>768</v>
       </c>
     </row>
     <row r="10">
@@ -8414,19 +8414,19 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>400</v>
+        <v>480</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="D10" s="38" t="n">
-        <v>600</v>
+        <v>720</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>700</v>
+        <v>840</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>800</v>
+        <v>960</v>
       </c>
     </row>
     <row r="12">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="C13" s="37" t="inlineStr">
         <is>
-          <t>5社</t>
+          <t>5社 ★BEP</t>
         </is>
       </c>
       <c r="D13" s="33" t="inlineStr">
         <is>
-          <t>6社 ★BEP</t>
+          <t>6社</t>
         </is>
       </c>
       <c r="E13" s="37" t="inlineStr">
@@ -8475,19 +8475,19 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>96</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15">
@@ -8497,19 +8497,19 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="D15" s="38" t="n">
-        <v>124</v>
+        <v>164</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>158</v>
+        <v>206</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>192</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16">
@@ -8519,19 +8519,19 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>135</v>
+        <v>186</v>
       </c>
       <c r="D16" s="38" t="n">
-        <v>186</v>
+        <v>246</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>237</v>
+        <v>309</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>288</v>
+        <v>369</v>
       </c>
     </row>
     <row r="17">
@@ -8541,19 +8541,19 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>112</v>
+        <v>168</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="D17" s="38" t="n">
-        <v>248</v>
+        <v>328</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>316</v>
+        <v>412</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>384</v>
+        <v>492</v>
       </c>
     </row>
     <row r="18">
@@ -8563,19 +8563,19 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>225</v>
+        <v>310</v>
       </c>
       <c r="D18" s="38" t="n">
-        <v>310</v>
+        <v>410</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>395</v>
+        <v>515</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>480</v>
+        <v>615</v>
       </c>
     </row>
     <row r="20">
@@ -9073,7 +9073,7 @@
     <row r="44">
       <c r="A44" s="87" t="inlineStr">
         <is>
-          <t>▌FDE変動報酬（インセンティブ制）試算  ─  固定給45万 → 基本給35万 + 担当社数インセンティブ（6社以上で+10万）</t>
+          <t>▌FDE変動報酬（インセンティブ制）試算  ─  固定給45万 → 基本給35万 + 担当社数インセンティブ（5社以上で+10万）</t>
         </is>
       </c>
     </row>
@@ -9117,12 +9117,12 @@
     <row r="46">
       <c r="A46" s="93" t="inlineStr">
         <is>
-          <t>オンボーディング（0〜5社）</t>
+          <t>オンボーディング（0〜4社）</t>
         </is>
       </c>
       <c r="B46" s="94" t="inlineStr">
         <is>
-          <t>0〜5社</t>
+          <t>0〜4社</t>
         </is>
       </c>
       <c r="C46" s="94" t="inlineStr">
@@ -9154,12 +9154,12 @@
     <row r="47">
       <c r="A47" s="54" t="inlineStr">
         <is>
-          <t>フル稼働（6社達成）</t>
+          <t>フル稼働（5社達成）</t>
         </is>
       </c>
       <c r="B47" s="56" t="inlineStr">
         <is>
-          <t>6社以上</t>
+          <t>5社以上</t>
         </is>
       </c>
       <c r="C47" s="56" t="inlineStr">
@@ -9191,12 +9191,12 @@
     <row r="48">
       <c r="A48" s="54" t="inlineStr">
         <is>
-          <t>超過達成（7〜8社）</t>
+          <t>超過達成（6〜8社）</t>
         </is>
       </c>
       <c r="B48" s="56" t="inlineStr">
         <is>
-          <t>7〜8社</t>
+          <t>6〜8社</t>
         </is>
       </c>
       <c r="C48" s="56" t="inlineStr">
@@ -9265,7 +9265,7 @@
     <row r="50">
       <c r="A50" s="92" t="inlineStr">
         <is>
-          <t>※ 変動報酬制の主効果: 採用直後の固定費バーンレート低減（超保守シナリオの悲観度が改善）。6社達成後は固定給と同額のため高パフォーマーの不満なし。達成インセンティブがFDE稼働率・顧客満足度向上に連鎖。</t>
+          <t>※ 変動報酬制の主効果: 採用直後の固定費バーンレート低減（超保守シナリオの悲観度が改善）。5社達成後は固定給と同額のため高パフォーマーの不満なし。達成インセンティブがFDE稼働率・顧客満足度向上に連鎖。</t>
         </is>
       </c>
     </row>
@@ -9275,8 +9275,8 @@
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A50:G50"/>
     <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A50:G50"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A4:I4"/>

--- a/financial/UNLID_財務モデル_v4.9.xlsx
+++ b/financial/UNLID_財務モデル_v4.9.xlsx
@@ -8283,7 +8283,7 @@
     <row r="4">
       <c r="A4" s="36" t="inlineStr">
         <is>
-          <t>▌月商マトリックス（万円/月）  ─  単価：24万円/社 固定</t>
+          <t>▌月商マトリックス（万円/月）  ─  単価：20万円/社 固定</t>
         </is>
       </c>
     </row>
@@ -8300,12 +8300,12 @@
       </c>
       <c r="C5" s="37" t="inlineStr">
         <is>
-          <t>5社 ★BEP</t>
+          <t>5社</t>
         </is>
       </c>
       <c r="D5" s="33" t="inlineStr">
         <is>
-          <t>6社</t>
+          <t>6社 ★BEP</t>
         </is>
       </c>
       <c r="E5" s="37" t="inlineStr">
@@ -8326,19 +8326,19 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C6" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" s="8" t="n">
         <v>120</v>
       </c>
-      <c r="D6" s="8" t="n">
-        <v>144</v>
-      </c>
       <c r="E6" s="6" t="n">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7">
@@ -8348,19 +8348,19 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="C7" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="D7" s="38" t="n">
         <v>240</v>
       </c>
-      <c r="D7" s="38" t="n">
-        <v>288</v>
-      </c>
       <c r="E7" s="6" t="n">
-        <v>336</v>
+        <v>280</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>384</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8">
@@ -8370,19 +8370,19 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="C8" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="D8" s="38" t="n">
         <v>360</v>
       </c>
-      <c r="D8" s="38" t="n">
-        <v>432</v>
-      </c>
       <c r="E8" s="6" t="n">
-        <v>504</v>
+        <v>420</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>576</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -8392,19 +8392,19 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>384</v>
+        <v>320</v>
       </c>
       <c r="C9" s="6" t="n">
+        <v>400</v>
+      </c>
+      <c r="D9" s="38" t="n">
         <v>480</v>
       </c>
-      <c r="D9" s="38" t="n">
-        <v>576</v>
-      </c>
       <c r="E9" s="6" t="n">
-        <v>672</v>
+        <v>560</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>768</v>
+        <v>640</v>
       </c>
     </row>
     <row r="10">
@@ -8414,19 +8414,19 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>480</v>
+        <v>400</v>
       </c>
       <c r="C10" s="6" t="n">
+        <v>500</v>
+      </c>
+      <c r="D10" s="38" t="n">
         <v>600</v>
       </c>
-      <c r="D10" s="38" t="n">
-        <v>720</v>
-      </c>
       <c r="E10" s="6" t="n">
-        <v>840</v>
+        <v>700</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>960</v>
+        <v>800</v>
       </c>
     </row>
     <row r="12">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="C13" s="37" t="inlineStr">
         <is>
-          <t>5社 ★BEP</t>
+          <t>5社</t>
         </is>
       </c>
       <c r="D13" s="33" t="inlineStr">
         <is>
-          <t>6社</t>
+          <t>6社 ★BEP</t>
         </is>
       </c>
       <c r="E13" s="37" t="inlineStr">
@@ -8475,19 +8475,19 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C14" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D14" s="8" t="n">
         <v>62</v>
       </c>
-      <c r="D14" s="8" t="n">
-        <v>82</v>
-      </c>
       <c r="E14" s="6" t="n">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>123</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -8497,19 +8497,19 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="C15" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="D15" s="38" t="n">
         <v>124</v>
       </c>
-      <c r="D15" s="38" t="n">
-        <v>164</v>
-      </c>
       <c r="E15" s="6" t="n">
-        <v>206</v>
+        <v>158</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>246</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16">
@@ -8519,19 +8519,19 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="C16" s="6" t="n">
+        <v>135</v>
+      </c>
+      <c r="D16" s="38" t="n">
         <v>186</v>
       </c>
-      <c r="D16" s="38" t="n">
-        <v>246</v>
-      </c>
       <c r="E16" s="6" t="n">
-        <v>309</v>
+        <v>237</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>369</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17">
@@ -8541,19 +8541,19 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>168</v>
+        <v>112</v>
       </c>
       <c r="C17" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="D17" s="38" t="n">
         <v>248</v>
       </c>
-      <c r="D17" s="38" t="n">
-        <v>328</v>
-      </c>
       <c r="E17" s="6" t="n">
-        <v>412</v>
+        <v>316</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>492</v>
+        <v>384</v>
       </c>
     </row>
     <row r="18">
@@ -8563,19 +8563,19 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="C18" s="6" t="n">
+        <v>225</v>
+      </c>
+      <c r="D18" s="38" t="n">
         <v>310</v>
       </c>
-      <c r="D18" s="38" t="n">
-        <v>410</v>
-      </c>
       <c r="E18" s="6" t="n">
-        <v>515</v>
+        <v>395</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>615</v>
+        <v>480</v>
       </c>
     </row>
     <row r="20">
@@ -9073,7 +9073,7 @@
     <row r="44">
       <c r="A44" s="87" t="inlineStr">
         <is>
-          <t>▌FDE変動報酬（インセンティブ制）試算  ─  固定給45万 → 基本給35万 + 担当社数インセンティブ（5社以上で+10万）</t>
+          <t>▌FDE変動報酬（インセンティブ制）試算  ─  固定給45万 → 基本給35万 + 担当社数インセンティブ（6社以上で+10万）</t>
         </is>
       </c>
     </row>
@@ -9117,12 +9117,12 @@
     <row r="46">
       <c r="A46" s="93" t="inlineStr">
         <is>
-          <t>オンボーディング（0〜4社）</t>
+          <t>オンボーディング（0〜5社）</t>
         </is>
       </c>
       <c r="B46" s="94" t="inlineStr">
         <is>
-          <t>0〜4社</t>
+          <t>0〜5社</t>
         </is>
       </c>
       <c r="C46" s="94" t="inlineStr">
@@ -9154,12 +9154,12 @@
     <row r="47">
       <c r="A47" s="54" t="inlineStr">
         <is>
-          <t>フル稼働（5社達成）</t>
+          <t>フル稼働（6社達成）</t>
         </is>
       </c>
       <c r="B47" s="56" t="inlineStr">
         <is>
-          <t>5社以上</t>
+          <t>6社以上</t>
         </is>
       </c>
       <c r="C47" s="56" t="inlineStr">
@@ -9191,12 +9191,12 @@
     <row r="48">
       <c r="A48" s="54" t="inlineStr">
         <is>
-          <t>超過達成（6〜8社）</t>
+          <t>超過達成（7〜8社）</t>
         </is>
       </c>
       <c r="B48" s="56" t="inlineStr">
         <is>
-          <t>6〜8社</t>
+          <t>7〜8社</t>
         </is>
       </c>
       <c r="C48" s="56" t="inlineStr">
@@ -9265,7 +9265,7 @@
     <row r="50">
       <c r="A50" s="92" t="inlineStr">
         <is>
-          <t>※ 変動報酬制の主効果: 採用直後の固定費バーンレート低減（超保守シナリオの悲観度が改善）。5社達成後は固定給と同額のため高パフォーマーの不満なし。達成インセンティブがFDE稼働率・顧客満足度向上に連鎖。</t>
+          <t>※ 変動報酬制の主効果: 採用直後の固定費バーンレート低減（超保守シナリオの悲観度が改善）。6社達成後は固定給と同額のため高パフォーマーの不満なし。達成インセンティブがFDE稼働率・顧客満足度向上に連鎖。</t>
         </is>
       </c>
     </row>

--- a/financial/UNLID_財務モデル_v4.9.xlsx
+++ b/financial/UNLID_財務モデル_v4.9.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,6 +97,9 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="29">
@@ -302,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -580,6 +583,10 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -946,7 +953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2554,6 +2561,152 @@
       <c r="A112" t="inlineStr">
         <is>
           <t>銀行借入2,000万円はY2シード調達（3,000万円）後に余剰資金で早期返済も可能。LTV/CAC = 380万/12万 = 31.7倍。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="96" t="inlineStr">
+        <is>
+          <t>⑪ FDE1名あたり稼働設計前提（6社担当の実現根拠）</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="96" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B116" s="96" t="inlineStr">
+        <is>
+          <t>詳細</t>
+        </is>
+      </c>
+      <c r="C116" s="96" t="inlineStr">
+        <is>
+          <t>時間数</t>
+        </is>
+      </c>
+      <c r="D116" s="96" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>打ち合わせ・直接実作業（1社あたり）</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>顧客との定例MTG・AI設計レビュー・成果確認</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>週1〜2時間</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>オンライン30〜60分×週1〜2回</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>ワーカー連携・進捗管理（1社あたり）</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>ワーカーへのタスク指示・成果レビュー・フィードバック</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>週3時間</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>チャット指示1h＋成果確認2h程度</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="96" t="inlineStr">
+        <is>
+          <t>★ 1社あたり合計稼働（FDE）</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>打ち合わせ1〜2h + ワーカー連携3h</t>
+        </is>
+      </c>
+      <c r="C119" s="96" t="inlineStr">
+        <is>
+          <t>週5時間 / 社</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>8時間（1人日）は超えない設計</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>6社担当時の合計稼働</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>6社 × 週5時間</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>週30時間（月120時間）</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>フルタイム正社員の標準160h/月に対し、余裕40h残存</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ワーカー実務時間（FDE稼働とは別）</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>実装・データ処理・資料作成等（副業ワーカー担当）</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>月20〜30時間 / 社</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>時給1,500円 × 20〜30h × 6社 = △18〜27万円/月</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="97" t="inlineStr">
+        <is>
+          <t>※ FDEは「設計・監督・判断」に特化。実作業をワーカーに委譲することで6社同時担当を実現。週30hの余裕時間で社内業務・採用・戦略立案に充当可能。リブ・コンサルティング（6〜8社/コンサルタント）の実績とも整合する担当社数設計。</t>
         </is>
       </c>
     </row>
